--- a/results_(stress_test)_PCCxSigmoid-PLV-/cnn_evaluation(stress_test)_k-10_p-30_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLV-/cnn_evaluation(stress_test)_k-10_p-30_nm_basis-False_nm_modifier-False.xlsx
@@ -12,6 +12,8 @@
     <sheet name="summary_t" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="nrr_32" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="nrr_16" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="nrr_8" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="nrr_4" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1078,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1219,82 @@
         <v>3.942217338903269</v>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>75.88266334483863</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75.45798610504099</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6020133713556465</v>
+      </c>
+      <c r="D8" t="n">
+        <v>75.88266334483863</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8.493458778165067</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8.762284989433915</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1946851840602061</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.493458778165067</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>56.96150197377717</v>
+      </c>
+      <c r="B10" t="n">
+        <v>54.88932128403399</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.003250397086764</v>
+      </c>
+      <c r="D10" t="n">
+        <v>56.96150197377717</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8.712131660455469</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9.624042680572741</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1817749539837845</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.712131660455469</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Std</t>
         </is>
@@ -1233,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,6 +1432,58 @@
       </c>
       <c r="H4" t="n">
         <v>0.1979747285109176</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>75.88266334483863</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8.493458778165067</v>
+      </c>
+      <c r="C5" t="n">
+        <v>75.45798610504099</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.762284989433915</v>
+      </c>
+      <c r="E5" t="n">
+        <v>75.88266334483863</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.493458778165067</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6020133713556465</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1946851840602061</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>56.96150197377717</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8.712131660455469</v>
+      </c>
+      <c r="C6" t="n">
+        <v>54.88932128403399</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.624042680572741</v>
+      </c>
+      <c r="E6" t="n">
+        <v>56.96150197377717</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.712131660455469</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.003250397086764</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1817749539837845</v>
       </c>
     </row>
   </sheetData>
@@ -2657,4 +2787,1302 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>78.98018148945926</v>
+      </c>
+      <c r="C2" t="n">
+        <v>78.43917490412591</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5389551963967582</v>
+      </c>
+      <c r="E2" t="n">
+        <v>78.98018148945926</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>79.66833623128227</v>
+      </c>
+      <c r="C3" t="n">
+        <v>79.44700036627356</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5260029335195819</v>
+      </c>
+      <c r="E3" t="n">
+        <v>79.66833623128227</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>79.12629001980986</v>
+      </c>
+      <c r="C4" t="n">
+        <v>78.90539351312434</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5011811763358612</v>
+      </c>
+      <c r="E4" t="n">
+        <v>79.12629001980986</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>69.64973745447625</v>
+      </c>
+      <c r="C5" t="n">
+        <v>68.99044910100186</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6969707186023395</v>
+      </c>
+      <c r="E5" t="n">
+        <v>69.64973745447625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>67.90448014256178</v>
+      </c>
+      <c r="C6" t="n">
+        <v>67.62200429017057</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7869253307580948</v>
+      </c>
+      <c r="E6" t="n">
+        <v>67.90448014256178</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60.74723829790916</v>
+      </c>
+      <c r="C7" t="n">
+        <v>60.19816347605863</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.916494420170784</v>
+      </c>
+      <c r="E7" t="n">
+        <v>60.74723829790916</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>80.54273825898147</v>
+      </c>
+      <c r="C8" t="n">
+        <v>80.3058652945352</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4926728925197191</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80.54273825898147</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>82.96680767134663</v>
+      </c>
+      <c r="C9" t="n">
+        <v>82.9317688922639</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4403832150623203</v>
+      </c>
+      <c r="E9" t="n">
+        <v>82.96680767134663</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>88.17835794427288</v>
+      </c>
+      <c r="C10" t="n">
+        <v>88.23909596391408</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3085805489992102</v>
+      </c>
+      <c r="E10" t="n">
+        <v>88.17835794427288</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>85.20869557695136</v>
+      </c>
+      <c r="C11" t="n">
+        <v>85.25452756458678</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3952541222951064</v>
+      </c>
+      <c r="E11" t="n">
+        <v>85.20869557695136</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>78.2966980683224</v>
+      </c>
+      <c r="C12" t="n">
+        <v>78.26223343089032</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.568648990492026</v>
+      </c>
+      <c r="E12" t="n">
+        <v>78.2966980683224</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>80.46583447953702</v>
+      </c>
+      <c r="C13" t="n">
+        <v>80.21020016434531</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5654270206267635</v>
+      </c>
+      <c r="E13" t="n">
+        <v>80.46583447953702</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>64.46111125528768</v>
+      </c>
+      <c r="C14" t="n">
+        <v>63.40048314386811</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8086384524901709</v>
+      </c>
+      <c r="E14" t="n">
+        <v>64.46111125528768</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>66.92826062509191</v>
+      </c>
+      <c r="C15" t="n">
+        <v>66.98990938840736</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7168797393639883</v>
+      </c>
+      <c r="E15" t="n">
+        <v>66.92826062509191</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>65.53767766157146</v>
+      </c>
+      <c r="C16" t="n">
+        <v>64.69453160101554</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8658064802487692</v>
+      </c>
+      <c r="E16" t="n">
+        <v>65.53767766157146</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>77.10144551423454</v>
+      </c>
+      <c r="C17" t="n">
+        <v>76.68672225007465</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5658279517665505</v>
+      </c>
+      <c r="E17" t="n">
+        <v>77.10144551423454</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>76.13629875690967</v>
+      </c>
+      <c r="C18" t="n">
+        <v>74.98353126465288</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6949359671523173</v>
+      </c>
+      <c r="E18" t="n">
+        <v>76.13629875690967</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>86.61026479467816</v>
+      </c>
+      <c r="C19" t="n">
+        <v>86.62447484111109</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.354559134071072</v>
+      </c>
+      <c r="E19" t="n">
+        <v>86.61026479467816</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>73.0299570065485</v>
+      </c>
+      <c r="C20" t="n">
+        <v>72.27243162841518</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6501501726141821</v>
+      </c>
+      <c r="E20" t="n">
+        <v>73.0299570065485</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>65.36899108123774</v>
+      </c>
+      <c r="C21" t="n">
+        <v>64.00005745829165</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8802942619969448</v>
+      </c>
+      <c r="E21" t="n">
+        <v>65.36899108123774</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="C22" t="n">
+        <v>74.76834602781143</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5863067835569382</v>
+      </c>
+      <c r="E22" t="n">
+        <v>75.45454545454545</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>66.85568214257908</v>
+      </c>
+      <c r="C23" t="n">
+        <v>65.76539666951541</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.829741129030784</v>
+      </c>
+      <c r="E23" t="n">
+        <v>66.85568214257908</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>78.42749504753502</v>
+      </c>
+      <c r="C24" t="n">
+        <v>78.1860247173851</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5234486196190119</v>
+      </c>
+      <c r="E24" t="n">
+        <v>78.42749504753502</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>73.0037457071428</v>
+      </c>
+      <c r="C25" t="n">
+        <v>72.63868331960718</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.6109001062810421</v>
+      </c>
+      <c r="E25" t="n">
+        <v>73.0037457071428</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>77.03760413152364</v>
+      </c>
+      <c r="C26" t="n">
+        <v>77.1307126858368</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5581483460962773</v>
+      </c>
+      <c r="E26" t="n">
+        <v>77.03760413152364</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>59.13615169681399</v>
+      </c>
+      <c r="C27" t="n">
+        <v>58.34909677749302</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.048762009789546</v>
+      </c>
+      <c r="E27" t="n">
+        <v>59.13615169681399</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>73.44034117942196</v>
+      </c>
+      <c r="C28" t="n">
+        <v>72.58013470197565</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.687539250900348</v>
+      </c>
+      <c r="E28" t="n">
+        <v>73.44034117942196</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>84.51950276386474</v>
+      </c>
+      <c r="C29" t="n">
+        <v>84.4580675946778</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3984711127355695</v>
+      </c>
+      <c r="E29" t="n">
+        <v>84.51950276386474</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>89.95172968624296</v>
+      </c>
+      <c r="C30" t="n">
+        <v>89.92387070611888</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.3014517015208791</v>
+      </c>
+      <c r="E30" t="n">
+        <v>89.95172968624296</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>91.74370020501908</v>
+      </c>
+      <c r="C31" t="n">
+        <v>91.481231413681</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2410433556564385</v>
+      </c>
+      <c r="E31" t="n">
+        <v>91.74370020501908</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>75.88266334483863</v>
+      </c>
+      <c r="C32" t="n">
+        <v>75.45798610504099</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.6020133713556465</v>
+      </c>
+      <c r="E32" t="n">
+        <v>75.88266334483863</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8.493458778165067</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8.762284989433915</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1946851840602061</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.493458778165067</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>60.1598629745932</v>
+      </c>
+      <c r="C2" t="n">
+        <v>59.06802868059607</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9112336784601212</v>
+      </c>
+      <c r="E2" t="n">
+        <v>60.1598629745932</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>56.66286040536683</v>
+      </c>
+      <c r="C3" t="n">
+        <v>54.57294675410641</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.021230404575666</v>
+      </c>
+      <c r="E3" t="n">
+        <v>56.66286040536683</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>61.42899160027336</v>
+      </c>
+      <c r="C4" t="n">
+        <v>60.24203954386504</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8812456597884497</v>
+      </c>
+      <c r="E4" t="n">
+        <v>61.42899160027336</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>47.09487106289846</v>
+      </c>
+      <c r="C5" t="n">
+        <v>43.97302218845594</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.174143479019403</v>
+      </c>
+      <c r="E5" t="n">
+        <v>47.09487106289847</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>50.72985060424399</v>
+      </c>
+      <c r="C6" t="n">
+        <v>46.11391910876172</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.18434759726127</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50.72985060424399</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>46.84140866270469</v>
+      </c>
+      <c r="C7" t="n">
+        <v>43.05938569167571</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.214608609676361</v>
+      </c>
+      <c r="E7" t="n">
+        <v>46.84140866270469</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>65.78802584797447</v>
+      </c>
+      <c r="C8" t="n">
+        <v>65.11600286157555</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8056578007837137</v>
+      </c>
+      <c r="E8" t="n">
+        <v>65.78802584797447</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>65.28966513551156</v>
+      </c>
+      <c r="C9" t="n">
+        <v>64.31829227852668</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8583680272102356</v>
+      </c>
+      <c r="E9" t="n">
+        <v>65.28966513551156</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>64.73230737290115</v>
+      </c>
+      <c r="C10" t="n">
+        <v>63.43160132069283</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7829236706097922</v>
+      </c>
+      <c r="E10" t="n">
+        <v>64.73230737290115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>56.68301628906825</v>
+      </c>
+      <c r="C11" t="n">
+        <v>54.61619247911234</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.07294161816438</v>
+      </c>
+      <c r="E11" t="n">
+        <v>56.68301628906825</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>47.05049351637989</v>
+      </c>
+      <c r="C12" t="n">
+        <v>44.68663765232345</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.217148142556349</v>
+      </c>
+      <c r="E12" t="n">
+        <v>47.05049351637989</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>56.78483377883892</v>
+      </c>
+      <c r="C13" t="n">
+        <v>55.14881538900481</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.013137509425481</v>
+      </c>
+      <c r="E13" t="n">
+        <v>56.78483377883892</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>49.19834946669089</v>
+      </c>
+      <c r="C14" t="n">
+        <v>47.23481619272983</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.053683664401372</v>
+      </c>
+      <c r="E14" t="n">
+        <v>49.19834946669089</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>49.86643483075113</v>
+      </c>
+      <c r="C15" t="n">
+        <v>48.29134974984305</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.087992761532466</v>
+      </c>
+      <c r="E15" t="n">
+        <v>49.86643483075113</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>48.43398299293246</v>
+      </c>
+      <c r="C16" t="n">
+        <v>46.03942006326319</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.08742263118426</v>
+      </c>
+      <c r="E16" t="n">
+        <v>48.43398299293246</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>57.22367840552253</v>
+      </c>
+      <c r="C17" t="n">
+        <v>54.2838163403715</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.047631805886825</v>
+      </c>
+      <c r="E17" t="n">
+        <v>57.22367840552253</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>61.50061851746123</v>
+      </c>
+      <c r="C18" t="n">
+        <v>59.19141681727636</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8405684195458889</v>
+      </c>
+      <c r="E18" t="n">
+        <v>61.50061851746123</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>62.35477815552038</v>
+      </c>
+      <c r="C19" t="n">
+        <v>61.43139556378848</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9033011108636856</v>
+      </c>
+      <c r="E19" t="n">
+        <v>62.35477815552038</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>57.32679348437271</v>
+      </c>
+      <c r="C20" t="n">
+        <v>56.02543540966062</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.030224659045537</v>
+      </c>
+      <c r="E20" t="n">
+        <v>57.32679348437271</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>51.90927257156204</v>
+      </c>
+      <c r="C21" t="n">
+        <v>50.42755622003062</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.165397479136785</v>
+      </c>
+      <c r="E21" t="n">
+        <v>51.90927257156204</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>58.26131713942162</v>
+      </c>
+      <c r="C22" t="n">
+        <v>57.6974681378458</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.94526908993721</v>
+      </c>
+      <c r="E22" t="n">
+        <v>58.26131713942162</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>50.34533170702169</v>
+      </c>
+      <c r="C23" t="n">
+        <v>48.13389549189846</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.137457929054896</v>
+      </c>
+      <c r="E23" t="n">
+        <v>50.34533170702169</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>45.55679547400929</v>
+      </c>
+      <c r="C24" t="n">
+        <v>40.64189379559351</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.340932871898015</v>
+      </c>
+      <c r="E24" t="n">
+        <v>45.55679547400929</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>44.66111298540645</v>
+      </c>
+      <c r="C25" t="n">
+        <v>39.8316416093006</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.216359915335973</v>
+      </c>
+      <c r="E25" t="n">
+        <v>44.66111298540645</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>59.96496509485375</v>
+      </c>
+      <c r="C26" t="n">
+        <v>56.65350047830035</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.9933374859392643</v>
+      </c>
+      <c r="E26" t="n">
+        <v>59.96496509485375</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>53.4978676286127</v>
+      </c>
+      <c r="C27" t="n">
+        <v>52.75471814841914</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.007581555843353</v>
+      </c>
+      <c r="E27" t="n">
+        <v>53.49786762861271</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>54.00937724374778</v>
+      </c>
+      <c r="C28" t="n">
+        <v>50.41201354949888</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.151840254664421</v>
+      </c>
+      <c r="E28" t="n">
+        <v>54.00937724374778</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>71.09845240875786</v>
+      </c>
+      <c r="C29" t="n">
+        <v>70.2320059892163</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7237688235938549</v>
+      </c>
+      <c r="E29" t="n">
+        <v>71.09845240875786</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>71.35390444554018</v>
+      </c>
+      <c r="C30" t="n">
+        <v>70.21106033135223</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7462223107616107</v>
+      </c>
+      <c r="E30" t="n">
+        <v>71.35390444554018</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>83.03583941037553</v>
+      </c>
+      <c r="C31" t="n">
+        <v>82.83935068393397</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4815329464462896</v>
+      </c>
+      <c r="E31" t="n">
+        <v>83.03583941037553</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>56.96150197377717</v>
+      </c>
+      <c r="C32" t="n">
+        <v>54.88932128403399</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.003250397086764</v>
+      </c>
+      <c r="E32" t="n">
+        <v>56.96150197377717</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8.712131660455469</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9.624042680572741</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1817749539837845</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.712131660455469</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>